--- a/docs/StructureDefinition-environmental-conditions.xlsx
+++ b/docs/StructureDefinition-environmental-conditions.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-30T19:11:20-07:00</t>
+    <t>2026-02-02T11:11:20-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-environmental-conditions.xlsx
+++ b/docs/StructureDefinition-environmental-conditions.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T11:11:20-06:00</t>
+    <t>2026-02-04T10:26:00-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-environmental-conditions.xlsx
+++ b/docs/StructureDefinition-environmental-conditions.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T00:24:16-05:00</t>
+    <t>2026-05-25T15:07:02-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-environmental-conditions.xlsx
+++ b/docs/StructureDefinition-environmental-conditions.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-environmental-conditions.xlsx
+++ b/docs/StructureDefinition-environmental-conditions.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="140">
   <si>
     <t>Property</t>
   </si>
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/environmental-conditions</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/environmental-conditions</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,6 +90,9 @@
     <t>Copyright</t>
   </si>
   <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
+  </si>
+  <si>
     <t>FHIR Version</t>
   </si>
   <si>
@@ -129,7 +132,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:Element</t>
+    <t>element:Procedure</t>
   </si>
   <si>
     <t>ID</t>
@@ -685,62 +688,64 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -793,123 +798,123 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -917,10 +922,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -932,7 +937,7 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L2" t="s" s="2">
         <v>9</v>
@@ -989,19 +994,19 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>20</v>
@@ -1009,10 +1014,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1020,10 +1025,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1035,13 +1040,13 @@
         <v>20</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1092,13 +1097,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -1107,26 +1112,26 @@
         <v>20</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -1138,16 +1143,16 @@
         <v>20</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
@@ -1185,55 +1190,55 @@
         <v>20</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
@@ -1245,13 +1250,13 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1302,19 +1307,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -1322,10 +1327,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1333,10 +1338,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -1348,13 +1353,13 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1405,13 +1410,13 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
@@ -1420,15 +1425,15 @@
         <v>20</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1436,10 +1441,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -1451,13 +1456,13 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1496,31 +1501,31 @@
         <v>20</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -1528,10 +1533,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1539,10 +1544,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -1554,16 +1559,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1571,7 +1576,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>20</v>
@@ -1613,13 +1618,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -1628,15 +1633,15 @@
         <v>20</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1644,10 +1649,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -1659,13 +1664,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1716,43 +1721,43 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
@@ -1764,13 +1769,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1821,19 +1826,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -1841,10 +1846,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1852,10 +1857,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -1867,13 +1872,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1924,13 +1929,13 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
@@ -1939,15 +1944,15 @@
         <v>20</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1955,10 +1960,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -1970,13 +1975,13 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2015,31 +2020,31 @@
         <v>20</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>20</v>
@@ -2047,10 +2052,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2058,10 +2063,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -2073,16 +2078,16 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2090,7 +2095,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>20</v>
@@ -2132,13 +2137,13 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
@@ -2147,15 +2152,15 @@
         <v>20</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2163,10 +2168,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -2178,13 +2183,13 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2235,43 +2240,43 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -2283,13 +2288,13 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2340,19 +2345,19 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>20</v>
@@ -2360,10 +2365,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2371,10 +2376,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -2386,13 +2391,13 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2443,13 +2448,13 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
@@ -2458,15 +2463,15 @@
         <v>20</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2474,10 +2479,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -2489,13 +2494,13 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2534,31 +2539,31 @@
         <v>20</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>20</v>
@@ -2566,10 +2571,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2577,10 +2582,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -2592,16 +2597,16 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2609,7 +2614,7 @@
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>20</v>
@@ -2651,13 +2656,13 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
@@ -2666,15 +2671,15 @@
         <v>20</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2682,10 +2687,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -2697,13 +2702,13 @@
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2754,43 +2759,43 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -2802,13 +2807,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2859,19 +2864,19 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>20</v>
@@ -2879,10 +2884,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2890,10 +2895,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -2905,13 +2910,13 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2962,13 +2967,13 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
@@ -2977,15 +2982,15 @@
         <v>20</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2993,10 +2998,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -3008,13 +3013,13 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3053,31 +3058,31 @@
         <v>20</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>20</v>
@@ -3085,10 +3090,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3096,10 +3101,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -3111,16 +3116,16 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3128,7 +3133,7 @@
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>20</v>
@@ -3170,13 +3175,13 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
@@ -3185,15 +3190,15 @@
         <v>20</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3201,10 +3206,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -3216,13 +3221,13 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3273,30 +3278,30 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3304,10 +3309,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -3319,16 +3324,16 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3378,13 +3383,13 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
@@ -3393,15 +3398,15 @@
         <v>20</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3409,10 +3414,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -3424,13 +3429,13 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3481,22 +3486,22 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
